--- a/scripts/fixtures/conciliacion.xlsx
+++ b/scripts/fixtures/conciliacion.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="76">
   <si>
     <t>Fecha emisión</t>
   </si>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t>Otros</t>
+  </si>
+  <si>
+    <t>Adicional (+)</t>
   </si>
   <si>
     <t>Otros concepto</t>
@@ -612,10 +615,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:W9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -682,22 +685,25 @@
       <c r="V1" t="s">
         <v>21</v>
       </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F2">
         <v>3000000</v>
@@ -709,45 +715,45 @@
         <v>3570000</v>
       </c>
       <c r="I2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2">
+        <v>30</v>
+      </c>
+      <c r="M2" t="s">
+        <v>31</v>
+      </c>
+      <c r="S2" t="s">
+        <v>32</v>
+      </c>
+      <c r="T2" t="s">
+        <v>32</v>
+      </c>
+      <c r="W2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" t="s">
         <v>27</v>
-      </c>
-      <c r="J2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2">
-        <v>30</v>
-      </c>
-      <c r="M2" t="s">
-        <v>30</v>
-      </c>
-      <c r="R2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S2" t="s">
-        <v>31</v>
-      </c>
-      <c r="V2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" t="s">
-        <v>26</v>
       </c>
       <c r="F3">
         <v>3000000</v>
@@ -759,45 +765,45 @@
         <v>3570000</v>
       </c>
       <c r="I3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3">
+        <v>30</v>
+      </c>
+      <c r="M3" t="s">
+        <v>38</v>
+      </c>
+      <c r="S3" t="s">
+        <v>32</v>
+      </c>
+      <c r="T3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" t="s">
         <v>27</v>
-      </c>
-      <c r="J3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3">
-        <v>30</v>
-      </c>
-      <c r="M3" t="s">
-        <v>37</v>
-      </c>
-      <c r="R3" t="s">
-        <v>31</v>
-      </c>
-      <c r="S3" t="s">
-        <v>31</v>
-      </c>
-      <c r="V3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" t="s">
-        <v>26</v>
       </c>
       <c r="F4">
         <v>3000000</v>
@@ -809,45 +815,45 @@
         <v>3570000</v>
       </c>
       <c r="I4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4">
+        <v>30</v>
+      </c>
+      <c r="M4" t="s">
+        <v>44</v>
+      </c>
+      <c r="S4" t="s">
+        <v>32</v>
+      </c>
+      <c r="T4" t="s">
+        <v>32</v>
+      </c>
+      <c r="W4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" t="s">
         <v>27</v>
-      </c>
-      <c r="J4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4">
-        <v>30</v>
-      </c>
-      <c r="M4" t="s">
-        <v>43</v>
-      </c>
-      <c r="R4" t="s">
-        <v>31</v>
-      </c>
-      <c r="S4" t="s">
-        <v>31</v>
-      </c>
-      <c r="V4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" t="s">
-        <v>26</v>
       </c>
       <c r="F5">
         <v>3000000</v>
@@ -859,45 +865,45 @@
         <v>3570000</v>
       </c>
       <c r="I5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L5">
+        <v>30</v>
+      </c>
+      <c r="M5" t="s">
+        <v>50</v>
+      </c>
+      <c r="S5" t="s">
+        <v>32</v>
+      </c>
+      <c r="T5" t="s">
+        <v>32</v>
+      </c>
+      <c r="W5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" t="s">
         <v>27</v>
-      </c>
-      <c r="J5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5">
-        <v>30</v>
-      </c>
-      <c r="M5" t="s">
-        <v>49</v>
-      </c>
-      <c r="R5" t="s">
-        <v>31</v>
-      </c>
-      <c r="S5" t="s">
-        <v>31</v>
-      </c>
-      <c r="V5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" t="s">
-        <v>26</v>
       </c>
       <c r="F6">
         <v>3000000</v>
@@ -909,45 +915,45 @@
         <v>3570000</v>
       </c>
       <c r="I6" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L6">
+        <v>30</v>
+      </c>
+      <c r="M6" t="s">
+        <v>56</v>
+      </c>
+      <c r="S6" t="s">
+        <v>32</v>
+      </c>
+      <c r="T6" t="s">
+        <v>32</v>
+      </c>
+      <c r="W6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" t="s">
         <v>27</v>
-      </c>
-      <c r="J6" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L6">
-        <v>30</v>
-      </c>
-      <c r="M6" t="s">
-        <v>55</v>
-      </c>
-      <c r="R6" t="s">
-        <v>31</v>
-      </c>
-      <c r="S6" t="s">
-        <v>31</v>
-      </c>
-      <c r="V6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" t="s">
-        <v>26</v>
       </c>
       <c r="F7">
         <v>3000000</v>
@@ -959,45 +965,45 @@
         <v>3570000</v>
       </c>
       <c r="I7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" t="s">
+        <v>30</v>
+      </c>
+      <c r="L7">
+        <v>30</v>
+      </c>
+      <c r="M7" t="s">
+        <v>62</v>
+      </c>
+      <c r="S7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T7" t="s">
+        <v>32</v>
+      </c>
+      <c r="W7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" t="s">
         <v>27</v>
-      </c>
-      <c r="J7" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7" t="s">
-        <v>29</v>
-      </c>
-      <c r="L7">
-        <v>30</v>
-      </c>
-      <c r="M7" t="s">
-        <v>61</v>
-      </c>
-      <c r="R7" t="s">
-        <v>31</v>
-      </c>
-      <c r="S7" t="s">
-        <v>31</v>
-      </c>
-      <c r="V7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E8" t="s">
-        <v>26</v>
       </c>
       <c r="F8">
         <v>3000000</v>
@@ -1009,45 +1015,45 @@
         <v>3570000</v>
       </c>
       <c r="I8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L8">
+        <v>30</v>
+      </c>
+      <c r="M8" t="s">
+        <v>68</v>
+      </c>
+      <c r="S8" t="s">
+        <v>32</v>
+      </c>
+      <c r="T8" t="s">
+        <v>32</v>
+      </c>
+      <c r="W8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" t="s">
         <v>27</v>
-      </c>
-      <c r="J8" t="s">
-        <v>28</v>
-      </c>
-      <c r="K8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L8">
-        <v>30</v>
-      </c>
-      <c r="M8" t="s">
-        <v>67</v>
-      </c>
-      <c r="R8" t="s">
-        <v>31</v>
-      </c>
-      <c r="S8" t="s">
-        <v>31</v>
-      </c>
-      <c r="V8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" t="s">
-        <v>26</v>
       </c>
       <c r="F9">
         <v>3000000</v>
@@ -1059,28 +1065,28 @@
         <v>3570000</v>
       </c>
       <c r="I9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L9">
         <v>30</v>
       </c>
       <c r="M9" t="s">
-        <v>73</v>
-      </c>
-      <c r="R9" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="S9" t="s">
-        <v>31</v>
-      </c>
-      <c r="V9" t="s">
-        <v>74</v>
+        <v>32</v>
+      </c>
+      <c r="T9" t="s">
+        <v>32</v>
+      </c>
+      <c r="W9" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
